--- a/jogos_2025-05-27.xlsx
+++ b/jogos_2025-05-27.xlsx
@@ -253,42 +253,42 @@
     <t>Quang Nam</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>Kuressaare</t>
+    <t>Trans</t>
   </si>
   <si>
     <t>El Bayadh</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
     <t>Sandviken</t>
   </si>
   <si>
     <t>Trelleborg</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
@@ -316,40 +316,40 @@
     <t>Hà Nội II</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
     <t>Binh Dinh</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>CS Constantine</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
   </si>
   <si>
     <t>Talleres Córdoba</t>
@@ -1288,37 +1288,37 @@
         <v>119</v>
       </c>
       <c r="L4">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="M4">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="O4">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P4">
         <v>9.5</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T4">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -1330,22 +1330,22 @@
         <v>9.5</v>
       </c>
       <c r="Z4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1354,10 +1354,10 @@
         <v>2</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>120</v>
@@ -1366,46 +1366,46 @@
         <v>120</v>
       </c>
       <c r="AL4">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AM4">
         <v>1.25</v>
       </c>
       <c r="AN4">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AQ4">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AR4">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AS4">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AT4">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="AU4">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="AV4">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AW4">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AX4">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AY4">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BC4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" s="3">
         <v>45804.3125</v>
@@ -1458,64 +1458,64 @@
         <v>119</v>
       </c>
       <c r="L5">
-        <v>2.01</v>
+        <v>3.72</v>
       </c>
       <c r="M5">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="N5">
-        <v>3.07</v>
+        <v>1.74</v>
       </c>
       <c r="O5">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="P5">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="W5">
+        <v>1.05</v>
+      </c>
+      <c r="X5">
         <v>1.04</v>
       </c>
-      <c r="X5">
-        <v>1.05</v>
-      </c>
       <c r="Y5">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA5">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AB5">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AD5">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
@@ -1524,10 +1524,10 @@
         <v>2</v>
       </c>
       <c r="AH5">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AI5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="s">
         <v>120</v>
@@ -1536,46 +1536,46 @@
         <v>120</v>
       </c>
       <c r="AL5">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AM5">
+        <v>1.2</v>
+      </c>
+      <c r="AN5">
         <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.7</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AS5">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AT5">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="AU5">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="AV5">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AW5">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AX5">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AY5">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1584,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="BC5">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="BD5" s="3">
         <v>45804.3125</v>
@@ -1628,64 +1628,64 @@
         <v>119</v>
       </c>
       <c r="L6">
-        <v>3.72</v>
+        <v>2.13</v>
       </c>
       <c r="M6">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N6">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V6">
-        <v>6.4</v>
+        <v>6.85</v>
       </c>
       <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
         <v>1.05</v>
       </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z6">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA6">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD6">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AE6">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
         <v>1.7</v>
@@ -1694,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="AH6">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
         <v>120</v>
@@ -1706,13 +1706,13 @@
         <v>120</v>
       </c>
       <c r="AL6">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="AM6">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN6">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1742,10 +1742,10 @@
         <v>1.67</v>
       </c>
       <c r="AX6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AY6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="BC6">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="BD6" s="3">
         <v>45804.3125</v>
@@ -1968,76 +1968,76 @@
         <v>119</v>
       </c>
       <c r="L8">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE8">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ8" t="s">
         <v>120</v>
@@ -2046,13 +2046,13 @@
         <v>120</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2094,10 +2094,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BD8" s="3">
         <v>45804.5</v>
@@ -2138,76 +2138,76 @@
         <v>119</v>
       </c>
       <c r="L9">
-        <v>6.5</v>
+        <v>2.33</v>
       </c>
       <c r="M9">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="N9">
-        <v>1.33</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD9">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE9">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ9" t="s">
         <v>120</v>
@@ -2216,13 +2216,13 @@
         <v>120</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD9" s="3">
         <v>45804.5</v>
@@ -2281,10 +2281,10 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>85</v>
@@ -2308,76 +2308,76 @@
         <v>119</v>
       </c>
       <c r="L10">
-        <v>2.81</v>
+        <v>1.61</v>
       </c>
       <c r="M10">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>2.09</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="s">
         <v>120</v>
@@ -2386,13 +2386,13 @@
         <v>120</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" s="3">
         <v>45804.54166666666</v>
@@ -2451,10 +2451,10 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
         <v>86</v>
@@ -2478,76 +2478,76 @@
         <v>119</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="s">
         <v>120</v>
@@ -2556,13 +2556,13 @@
         <v>120</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO11">
         <v>-1</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD11" s="3">
         <v>45804.54166666666</v>
@@ -2988,76 +2988,76 @@
         <v>119</v>
       </c>
       <c r="L14">
-        <v>1.19</v>
+        <v>3.45</v>
       </c>
       <c r="M14">
-        <v>4.91</v>
+        <v>3.39</v>
       </c>
       <c r="N14">
-        <v>7.81</v>
+        <v>1.88</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
         <v>120</v>
@@ -3066,13 +3066,13 @@
         <v>120</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO14">
         <v>-1</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD14" s="3">
         <v>45804.625</v>
@@ -3158,76 +3158,76 @@
         <v>119</v>
       </c>
       <c r="L15">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="M15">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N15">
-        <v>1.79</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC15">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="s">
         <v>120</v>
@@ -3236,13 +3236,13 @@
         <v>120</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AO15">
         <v>-1</v>
@@ -3284,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BD15" s="3">
         <v>45804.625</v>
@@ -3701,16 +3701,16 @@
         <v>8.75</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y18">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="Z18">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AA18">
         <v>2.7</v>
@@ -3746,7 +3746,7 @@
         <v>120</v>
       </c>
       <c r="AL18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AM18">
         <v>1.31</v>
@@ -3758,34 +3758,34 @@
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AS18">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AT18">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AU18">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AV18">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AW18">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AX18">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AY18">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AZ18">
         <v>0</v>

--- a/jogos_2025-05-27.xlsx
+++ b/jogos_2025-05-27.xlsx
@@ -253,15 +253,15 @@
     <t>Quang Nam</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
@@ -271,12 +271,12 @@
     <t>Tammeka</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
     <t>Trans</t>
   </si>
   <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
     <t>Sandviken</t>
   </si>
   <si>
@@ -298,33 +298,33 @@
     <t>América Mineiro</t>
   </si>
   <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
     <t>Sydney II</t>
   </si>
   <si>
     <t>Hà Nội II</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Binh Dinh</t>
   </si>
   <si>
@@ -334,12 +334,12 @@
     <t>Tallinna Kalev</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
@@ -361,16 +361,16 @@
     <t>Atlético GO</t>
   </si>
   <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
     <t>Universitario</t>
   </si>
   <si>
+    <t>Carabobo</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Carabobo</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -948,13 +948,13 @@
         <v>119</v>
       </c>
       <c r="L2">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="M2">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
         <v>1.53</v>
@@ -966,58 +966,58 @@
         <v>2.4</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="T2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>14.9</v>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AA2">
-        <v>5.3</v>
+        <v>6.35</v>
       </c>
       <c r="AB2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD2">
         <v>2.05</v>
       </c>
       <c r="AE2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF2">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH2">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="AI2">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>120</v>
@@ -1032,40 +1032,40 @@
         <v>1.2</v>
       </c>
       <c r="AN2">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AQ2">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AR2">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AS2">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AT2">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AU2">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="AV2">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AW2">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AX2">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AY2">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1118,76 +1118,76 @@
         <v>119</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
         <v>120</v>
@@ -1196,46 +1196,46 @@
         <v>120</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD3" s="3">
         <v>45804.29166666666</v>
@@ -1288,37 +1288,37 @@
         <v>119</v>
       </c>
       <c r="L4">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="M4">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="N4">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P4">
         <v>9.5</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V4">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -1330,22 +1330,22 @@
         <v>9.5</v>
       </c>
       <c r="Z4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AB4">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AE4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1354,10 +1354,10 @@
         <v>2</v>
       </c>
       <c r="AH4">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>120</v>
@@ -1366,46 +1366,46 @@
         <v>120</v>
       </c>
       <c r="AL4">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AM4">
         <v>1.25</v>
       </c>
       <c r="AN4">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="AS4">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AT4">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="AU4">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="AV4">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AW4">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AX4">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AY4">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BC4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" s="3">
         <v>45804.3125</v>
@@ -1458,64 +1458,64 @@
         <v>119</v>
       </c>
       <c r="L5">
-        <v>3.72</v>
+        <v>2.01</v>
       </c>
       <c r="M5">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="N5">
-        <v>1.74</v>
+        <v>3.07</v>
       </c>
       <c r="O5">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
+        <v>1.36</v>
+      </c>
+      <c r="S5">
+        <v>2.9</v>
+      </c>
+      <c r="T5">
+        <v>2.65</v>
+      </c>
+      <c r="U5">
+        <v>1.42</v>
+      </c>
+      <c r="V5">
+        <v>6.75</v>
+      </c>
+      <c r="W5">
+        <v>1.04</v>
+      </c>
+      <c r="X5">
+        <v>1.05</v>
+      </c>
+      <c r="Y5">
+        <v>9.5</v>
+      </c>
+      <c r="Z5">
+        <v>1.28</v>
+      </c>
+      <c r="AA5">
+        <v>3.55</v>
+      </c>
+      <c r="AB5">
+        <v>1.82</v>
+      </c>
+      <c r="AC5">
+        <v>1.88</v>
+      </c>
+      <c r="AD5">
+        <v>3.2</v>
+      </c>
+      <c r="AE5">
         <v>1.33</v>
-      </c>
-      <c r="S5">
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <v>2.6</v>
-      </c>
-      <c r="U5">
-        <v>1.44</v>
-      </c>
-      <c r="V5">
-        <v>6.4</v>
-      </c>
-      <c r="W5">
-        <v>1.05</v>
-      </c>
-      <c r="X5">
-        <v>1.04</v>
-      </c>
-      <c r="Y5">
-        <v>10</v>
-      </c>
-      <c r="Z5">
-        <v>1.25</v>
-      </c>
-      <c r="AA5">
-        <v>3.9</v>
-      </c>
-      <c r="AB5">
-        <v>1.75</v>
-      </c>
-      <c r="AC5">
-        <v>1.95</v>
-      </c>
-      <c r="AD5">
-        <v>3</v>
-      </c>
-      <c r="AE5">
-        <v>1.38</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
@@ -1524,10 +1524,10 @@
         <v>2</v>
       </c>
       <c r="AH5">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AI5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
         <v>120</v>
@@ -1536,46 +1536,46 @@
         <v>120</v>
       </c>
       <c r="AL5">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AM5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN5">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AR5">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AS5">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AT5">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="AU5">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="AV5">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AW5">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AX5">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AY5">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1584,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="BC5">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" s="3">
         <v>45804.3125</v>
@@ -1628,64 +1628,64 @@
         <v>119</v>
       </c>
       <c r="L6">
-        <v>2.13</v>
+        <v>3.72</v>
       </c>
       <c r="M6">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="O6">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="P6">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
+        <v>1.33</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.44</v>
+      </c>
+      <c r="V6">
+        <v>6.4</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>10</v>
+      </c>
+      <c r="Z6">
+        <v>1.25</v>
+      </c>
+      <c r="AA6">
+        <v>3.9</v>
+      </c>
+      <c r="AB6">
+        <v>1.75</v>
+      </c>
+      <c r="AC6">
+        <v>1.95</v>
+      </c>
+      <c r="AD6">
+        <v>3</v>
+      </c>
+      <c r="AE6">
         <v>1.38</v>
-      </c>
-      <c r="S6">
-        <v>2.8</v>
-      </c>
-      <c r="T6">
-        <v>2.8</v>
-      </c>
-      <c r="U6">
-        <v>1.38</v>
-      </c>
-      <c r="V6">
-        <v>6.85</v>
-      </c>
-      <c r="W6">
-        <v>1.04</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>9.5</v>
-      </c>
-      <c r="Z6">
-        <v>1.3</v>
-      </c>
-      <c r="AA6">
-        <v>3.45</v>
-      </c>
-      <c r="AB6">
-        <v>1.9</v>
-      </c>
-      <c r="AC6">
-        <v>1.8</v>
-      </c>
-      <c r="AD6">
-        <v>3.35</v>
-      </c>
-      <c r="AE6">
-        <v>1.3</v>
       </c>
       <c r="AF6">
         <v>1.7</v>
@@ -1694,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="AH6">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="s">
         <v>120</v>
@@ -1706,13 +1706,13 @@
         <v>120</v>
       </c>
       <c r="AL6">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="AM6">
+        <v>1.2</v>
+      </c>
+      <c r="AN6">
         <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.62</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1742,10 +1742,10 @@
         <v>1.67</v>
       </c>
       <c r="AX6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AY6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BC6">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="BD6" s="3">
         <v>45804.3125</v>
@@ -1798,76 +1798,76 @@
         <v>119</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
         <v>120</v>
@@ -1876,46 +1876,46 @@
         <v>120</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM7">
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1924,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD7" s="3">
         <v>45804.33333333334</v>
@@ -1968,13 +1968,13 @@
         <v>119</v>
       </c>
       <c r="L8">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="N8">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="O8">
         <v>3.4</v>
@@ -1992,34 +1992,34 @@
         <v>3.7</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="V8">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="W8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="Z8">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AA8">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AB8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC8">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AD8">
         <v>2.05</v>
@@ -2028,16 +2028,16 @@
         <v>1.65</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AH8">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AI8">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="s">
         <v>120</v>
@@ -2046,13 +2046,13 @@
         <v>120</v>
       </c>
       <c r="AL8">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AM8">
         <v>1.15</v>
       </c>
       <c r="AN8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2156,40 +2156,40 @@
         <v>1.95</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="Z9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA9">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC9">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AD9">
         <v>2.25</v>
@@ -2198,16 +2198,16 @@
         <v>1.57</v>
       </c>
       <c r="AF9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG9">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH9">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AI9">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AJ9" t="s">
         <v>120</v>
@@ -2216,13 +2216,13 @@
         <v>120</v>
       </c>
       <c r="AL9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM9">
         <v>1.25</v>
       </c>
       <c r="AN9">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2281,10 +2281,10 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>85</v>
@@ -2308,76 +2308,76 @@
         <v>119</v>
       </c>
       <c r="L10">
+        <v>2.95</v>
+      </c>
+      <c r="M10">
+        <v>3.11</v>
+      </c>
+      <c r="N10">
+        <v>2.18</v>
+      </c>
+      <c r="O10">
+        <v>2.27</v>
+      </c>
+      <c r="P10">
+        <v>7.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.86</v>
+      </c>
+      <c r="R10">
+        <v>1.55</v>
+      </c>
+      <c r="S10">
+        <v>2.25</v>
+      </c>
+      <c r="T10">
+        <v>3.6</v>
+      </c>
+      <c r="U10">
+        <v>1.25</v>
+      </c>
+      <c r="V10">
+        <v>12</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.13</v>
+      </c>
+      <c r="Y10">
+        <v>6</v>
+      </c>
+      <c r="Z10">
+        <v>1.55</v>
+      </c>
+      <c r="AA10">
+        <v>2.3</v>
+      </c>
+      <c r="AB10">
+        <v>2.17</v>
+      </c>
+      <c r="AC10">
         <v>1.61</v>
       </c>
-      <c r="M10">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <v>1.53</v>
-      </c>
-      <c r="P10">
-        <v>16</v>
-      </c>
-      <c r="Q10">
-        <v>2.5</v>
-      </c>
-      <c r="R10">
-        <v>1.22</v>
-      </c>
-      <c r="S10">
-        <v>3.7</v>
-      </c>
-      <c r="T10">
+      <c r="AD10">
+        <v>5.2</v>
+      </c>
+      <c r="AE10">
+        <v>1.13</v>
+      </c>
+      <c r="AF10">
         <v>2.05</v>
       </c>
-      <c r="U10">
+      <c r="AG10">
         <v>1.67</v>
       </c>
-      <c r="V10">
-        <v>4.3</v>
-      </c>
-      <c r="W10">
-        <v>1.17</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>16</v>
-      </c>
-      <c r="Z10">
-        <v>1.11</v>
-      </c>
-      <c r="AA10">
-        <v>5.2</v>
-      </c>
-      <c r="AB10">
-        <v>1.45</v>
-      </c>
-      <c r="AC10">
-        <v>2.55</v>
-      </c>
-      <c r="AD10">
-        <v>2.07</v>
-      </c>
-      <c r="AE10">
-        <v>1.67</v>
-      </c>
-      <c r="AF10">
-        <v>1.47</v>
-      </c>
-      <c r="AG10">
-        <v>2.4</v>
-      </c>
       <c r="AH10">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="AI10">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="s">
         <v>120</v>
@@ -2386,46 +2386,46 @@
         <v>120</v>
       </c>
       <c r="AL10">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AM10">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AN10">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="BC10">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="BD10" s="3">
         <v>45804.54166666666</v>
@@ -2451,10 +2451,10 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>86</v>
@@ -2478,76 +2478,76 @@
         <v>119</v>
       </c>
       <c r="L11">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="M11">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="Q11">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T11">
-        <v>3.26</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="V11">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AA11">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="AC11">
-        <v>1.61</v>
+        <v>2.65</v>
       </c>
       <c r="AD11">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="AE11">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AF11">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>8.5</v>
+        <v>3.95</v>
       </c>
       <c r="AI11">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="s">
         <v>120</v>
@@ -2556,13 +2556,13 @@
         <v>120</v>
       </c>
       <c r="AL11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM11">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AN11">
-        <v>1.28</v>
+        <v>2.54</v>
       </c>
       <c r="AO11">
         <v>-1</v>
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="BC11">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="BD11" s="3">
         <v>45804.54166666666</v>
@@ -3006,34 +3006,34 @@
         <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="T14">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V14">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>6.55</v>
       </c>
       <c r="Z14">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AA14">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB14">
         <v>1.89</v>
@@ -3042,22 +3042,22 @@
         <v>1.81</v>
       </c>
       <c r="AD14">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AE14">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG14">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AH14">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="AI14">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AJ14" t="s">
         <v>120</v>
@@ -3066,13 +3066,13 @@
         <v>120</v>
       </c>
       <c r="AL14">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AM14">
         <v>1.27</v>
       </c>
       <c r="AN14">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AO14">
         <v>-1</v>
@@ -3176,40 +3176,40 @@
         <v>4.15</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T15">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="V15">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA15">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AB15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC15">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AD15">
         <v>2.33</v>
@@ -3218,16 +3218,16 @@
         <v>1.54</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH15">
-        <v>3.85</v>
+        <v>5.75</v>
       </c>
       <c r="AI15">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="s">
         <v>120</v>
@@ -3236,46 +3236,46 @@
         <v>120</v>
       </c>
       <c r="AL15">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AM15">
         <v>1.12</v>
       </c>
       <c r="AN15">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3668,13 +3668,13 @@
         <v>119</v>
       </c>
       <c r="L18">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M18">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="N18">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
         <v>1.57</v>
@@ -3686,25 +3686,25 @@
         <v>2.88</v>
       </c>
       <c r="R18">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T18">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U18">
         <v>1.3</v>
       </c>
       <c r="V18">
-        <v>8.75</v>
+        <v>7.2</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y18">
         <v>7.5</v>
@@ -3716,28 +3716,28 @@
         <v>2.7</v>
       </c>
       <c r="AB18">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD18">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="AE18">
         <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH18">
         <v>8.5</v>
       </c>
       <c r="AI18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ18" t="s">
         <v>120</v>
@@ -3758,34 +3758,34 @@
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR18">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AS18">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AT18">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AV18">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AW18">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AX18">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AY18">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3838,76 +3838,76 @@
         <v>119</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="M19">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="N19">
-        <v>7.4</v>
+        <v>3.87</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA19">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="AB19">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD19">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE19">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH19">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI19">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="s">
         <v>120</v>
@@ -3916,46 +3916,46 @@
         <v>120</v>
       </c>
       <c r="AL19">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AM19">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AN19">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AR19">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AS19">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AT19">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AU19">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AV19">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AW19">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AX19">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AY19">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -3964,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="BC19">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="BD19" s="3">
         <v>45804.89583333334</v>
@@ -4008,64 +4008,64 @@
         <v>119</v>
       </c>
       <c r="L20">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="M20">
-        <v>3.69</v>
+        <v>4.7</v>
       </c>
       <c r="N20">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="O20">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>8.75</v>
+        <v>11</v>
       </c>
       <c r="Q20">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z20">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA20">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB20">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC20">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AD20">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AF20">
         <v>2</v>
@@ -4074,10 +4074,10 @@
         <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI20">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ20" t="s">
         <v>120</v>
@@ -4086,46 +4086,46 @@
         <v>120</v>
       </c>
       <c r="AL20">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AM20">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN20">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AR20">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AS20">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AT20">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AU20">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AV20">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AW20">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AX20">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AY20">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4134,10 +4134,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BC20">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="BD20" s="3">
         <v>45804.89583333334</v>
@@ -4178,76 +4178,76 @@
         <v>119</v>
       </c>
       <c r="L21">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="N21">
-        <v>3.87</v>
+        <v>14</v>
       </c>
       <c r="O21">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="P21">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T21">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U21">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V21">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AA21">
-        <v>3.65</v>
+        <v>5.25</v>
       </c>
       <c r="AB21">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC21">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="AD21">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AH21">
-        <v>5.75</v>
+        <v>3.85</v>
       </c>
       <c r="AI21">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AJ21" t="s">
         <v>120</v>
@@ -4256,46 +4256,46 @@
         <v>120</v>
       </c>
       <c r="AL21">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="AM21">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AN21">
-        <v>1.93</v>
+        <v>5.5</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AR21">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="AS21">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="AT21">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AU21">
-        <v>3.05</v>
+        <v>4.35</v>
       </c>
       <c r="AV21">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="AW21">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AX21">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AY21">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="BC21">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="BD21" s="3">
         <v>45804.89583333334</v>
@@ -4348,76 +4348,76 @@
         <v>119</v>
       </c>
       <c r="L22">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="M22">
-        <v>7.2</v>
+        <v>3.69</v>
       </c>
       <c r="N22">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="O22">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="P22">
-        <v>17</v>
+        <v>8.75</v>
       </c>
       <c r="Q22">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="R22">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T22">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA22">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB22">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="AD22">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AE22">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AI22">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AJ22" t="s">
         <v>120</v>
@@ -4426,46 +4426,46 @@
         <v>120</v>
       </c>
       <c r="AL22">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AM22">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AN22">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AQ22">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AR22">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="AS22">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AT22">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="AU22">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV22">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="AW22">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AX22">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AY22">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="BC22">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="BD22" s="3">
         <v>45804.89583333334</v>

--- a/jogos_2025-05-27.xlsx
+++ b/jogos_2025-05-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="129">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -253,130 +199,208 @@
     <t>Quang Nam</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Daegu</t>
   </si>
   <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Kuressaare</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>El Bayadh</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Trelleborg</t>
+    <t>CR Belouizdad</t>
   </si>
   <si>
     <t>JS Saoura</t>
   </si>
   <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Libertad</t>
   </si>
   <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>CSD Independiente del Valle</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Sydney II</t>
   </si>
   <si>
     <t>Hà Nội II</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
     <t>Binh Dinh</t>
   </si>
   <si>
+    <t>Tallinna Kalev</t>
+  </si>
+  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
     <t>CS Constantine</t>
   </si>
   <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
-    <t>Helsingborg</t>
+    <t>Paradou AC</t>
   </si>
   <si>
     <t>MC Alger</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>Talleres Córdoba</t>
   </si>
   <si>
+    <t>Atlético GO</t>
+  </si>
+  <si>
     <t>Alianza Lima</t>
   </si>
   <si>
-    <t>Atlético GO</t>
-  </si>
-  <si>
     <t>Barcelona</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
+    <t>Carabobo</t>
+  </si>
+  <si>
     <t>Universitario</t>
   </si>
   <si>
-    <t>Carabobo</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['56', '90+3']</t>
+  </si>
+  <si>
+    <t>['14']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['27', '31', '76', '87']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['19', '38', '49', '90+1']</t>
+  </si>
+  <si>
+    <t>['56', '77']</t>
+  </si>
+  <si>
+    <t>['26', '84']</t>
+  </si>
+  <si>
+    <t>['24', '28']</t>
+  </si>
+  <si>
+    <t>['45+5', '63']</t>
+  </si>
+  <si>
+    <t>['64', '69']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['10', '24']</t>
+  </si>
+  <si>
+    <t>['33', '37', '72']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['17', '45+6', '66', '71']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['34', '60', '90']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['74', '79']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['28', '42']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -740,10 +764,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD22"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,103 +882,49 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45804</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L2">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="M2">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N2">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
         <v>1.53</v>
@@ -966,144 +936,90 @@
         <v>2.4</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="W2">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z2">
         <v>1.05</v>
       </c>
       <c r="AA2">
-        <v>6.35</v>
+        <v>6.45</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AD2">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE2">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG2">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="AI2">
         <v>1.3</v>
       </c>
       <c r="AJ2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL2">
-        <v>1.25</v>
-      </c>
-      <c r="AM2">
-        <v>1.2</v>
-      </c>
-      <c r="AN2">
-        <v>1.62</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.39</v>
-      </c>
-      <c r="AQ2">
-        <v>1.71</v>
-      </c>
-      <c r="AR2">
-        <v>2.23</v>
-      </c>
-      <c r="AS2">
-        <v>2.97</v>
-      </c>
-      <c r="AT2">
-        <v>4.25</v>
-      </c>
-      <c r="AU2">
-        <v>2.59</v>
-      </c>
-      <c r="AV2">
-        <v>1.92</v>
-      </c>
-      <c r="AW2">
-        <v>1.55</v>
-      </c>
-      <c r="AX2">
-        <v>1.3</v>
-      </c>
-      <c r="AY2">
-        <v>1.15</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.53</v>
-      </c>
-      <c r="BC2">
-        <v>2.4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45804.27083333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45804</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1115,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L3">
         <v>2.27</v>
@@ -1190,135 +1106,81 @@
         <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3">
-        <v>1.36</v>
-      </c>
-      <c r="AM3">
-        <v>1.34</v>
-      </c>
-      <c r="AN3">
-        <v>1.4</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.47</v>
-      </c>
-      <c r="AQ3">
-        <v>1.8</v>
-      </c>
-      <c r="AR3">
-        <v>2.72</v>
-      </c>
-      <c r="AS3">
-        <v>3</v>
-      </c>
-      <c r="AT3">
-        <v>4.2</v>
-      </c>
-      <c r="AU3">
-        <v>2.5</v>
-      </c>
-      <c r="AV3">
-        <v>1.9</v>
-      </c>
-      <c r="AW3">
-        <v>1.55</v>
-      </c>
-      <c r="AX3">
-        <v>1.34</v>
-      </c>
-      <c r="AY3">
-        <v>1.19</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.8</v>
-      </c>
-      <c r="BC3">
-        <v>2.4</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45804.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45804</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L4">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="M4">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="O4">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P4">
         <v>9.5</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T4">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -1330,22 +1192,22 @@
         <v>9.5</v>
       </c>
       <c r="Z4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1354,141 +1216,87 @@
         <v>2</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL4">
-        <v>1.35</v>
-      </c>
-      <c r="AM4">
-        <v>1.25</v>
-      </c>
-      <c r="AN4">
-        <v>1.62</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.4</v>
-      </c>
-      <c r="AQ4">
-        <v>1.67</v>
-      </c>
-      <c r="AR4">
-        <v>2.07</v>
-      </c>
-      <c r="AS4">
-        <v>2.65</v>
-      </c>
-      <c r="AT4">
-        <v>3.55</v>
-      </c>
-      <c r="AU4">
-        <v>2.7</v>
-      </c>
-      <c r="AV4">
-        <v>2.07</v>
-      </c>
-      <c r="AW4">
-        <v>1.67</v>
-      </c>
-      <c r="AX4">
-        <v>1.41</v>
-      </c>
-      <c r="AY4">
-        <v>1.24</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.85</v>
-      </c>
-      <c r="BC4">
-        <v>2.2</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>118</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45804.3125</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45804</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L5">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="M5">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="N5">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P5">
         <v>9.5</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V5">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="W5">
         <v>1.04</v>
@@ -1500,22 +1308,22 @@
         <v>9.5</v>
       </c>
       <c r="Z5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AB5">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC5">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
@@ -1524,108 +1332,54 @@
         <v>2</v>
       </c>
       <c r="AH5">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL5">
-        <v>1.3</v>
-      </c>
-      <c r="AM5">
-        <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.7</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.53</v>
-      </c>
-      <c r="AQ5">
-        <v>1.9</v>
-      </c>
-      <c r="AR5">
-        <v>2.43</v>
-      </c>
-      <c r="AS5">
-        <v>3.2</v>
-      </c>
-      <c r="AT5">
-        <v>4.35</v>
-      </c>
-      <c r="AU5">
-        <v>2.32</v>
-      </c>
-      <c r="AV5">
-        <v>1.79</v>
-      </c>
-      <c r="AW5">
-        <v>1.48</v>
-      </c>
-      <c r="AX5">
-        <v>1.29</v>
-      </c>
-      <c r="AY5">
-        <v>1.17</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.77</v>
-      </c>
-      <c r="BC5">
-        <v>2.3</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>119</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45804.3125</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45804</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L6">
         <v>3.72</v>
@@ -1700,102 +1454,48 @@
         <v>1.13</v>
       </c>
       <c r="AJ6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s">
         <v>120</v>
       </c>
-      <c r="AL6">
-        <v>1.93</v>
-      </c>
-      <c r="AM6">
-        <v>1.2</v>
-      </c>
-      <c r="AN6">
-        <v>1.25</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>1.4</v>
-      </c>
-      <c r="AQ6">
-        <v>1.67</v>
-      </c>
-      <c r="AR6">
-        <v>2.07</v>
-      </c>
-      <c r="AS6">
-        <v>2.65</v>
-      </c>
-      <c r="AT6">
-        <v>3.55</v>
-      </c>
-      <c r="AU6">
-        <v>2.7</v>
-      </c>
-      <c r="AV6">
-        <v>2.07</v>
-      </c>
-      <c r="AW6">
-        <v>1.67</v>
-      </c>
-      <c r="AX6">
-        <v>1.42</v>
-      </c>
-      <c r="AY6">
-        <v>1.25</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.5</v>
-      </c>
-      <c r="BC6">
-        <v>1.65</v>
-      </c>
-      <c r="BD6" s="3">
+      <c r="AL6" s="3">
         <v>45804.3125</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45804</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L7">
         <v>2.29</v>
@@ -1870,451 +1570,289 @@
         <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL7">
-        <v>1.3</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1.65</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.44</v>
-      </c>
-      <c r="AQ7">
-        <v>1.75</v>
-      </c>
-      <c r="AR7">
-        <v>2.55</v>
-      </c>
-      <c r="AS7">
-        <v>2.85</v>
-      </c>
-      <c r="AT7">
-        <v>4</v>
-      </c>
-      <c r="AU7">
-        <v>2.6</v>
-      </c>
-      <c r="AV7">
-        <v>1.96</v>
-      </c>
-      <c r="AW7">
-        <v>1.59</v>
-      </c>
-      <c r="AX7">
-        <v>1.36</v>
-      </c>
-      <c r="AY7">
-        <v>1.2</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.62</v>
-      </c>
-      <c r="BC7">
-        <v>2.63</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>121</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45804.33333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45804</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L8">
-        <v>9.1</v>
+        <v>2.09</v>
       </c>
       <c r="M8">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="N8">
+        <v>2.87</v>
+      </c>
+      <c r="O8">
+        <v>1.9</v>
+      </c>
+      <c r="P8">
+        <v>14</v>
+      </c>
+      <c r="Q8">
+        <v>1.95</v>
+      </c>
+      <c r="R8">
         <v>1.23</v>
       </c>
-      <c r="O8">
-        <v>3.4</v>
-      </c>
-      <c r="P8">
-        <v>16.5</v>
-      </c>
-      <c r="Q8">
-        <v>1.34</v>
-      </c>
-      <c r="R8">
-        <v>1.22</v>
-      </c>
       <c r="S8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T8">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="V8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="W8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>13.4</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AA8">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AB8">
+        <v>1.5</v>
+      </c>
+      <c r="AC8">
+        <v>2.5</v>
+      </c>
+      <c r="AD8">
+        <v>2.21</v>
+      </c>
+      <c r="AE8">
+        <v>1.62</v>
+      </c>
+      <c r="AF8">
         <v>1.4</v>
       </c>
-      <c r="AC8">
-        <v>2.73</v>
-      </c>
-      <c r="AD8">
-        <v>2.05</v>
-      </c>
-      <c r="AE8">
-        <v>1.65</v>
-      </c>
-      <c r="AF8">
-        <v>2.05</v>
-      </c>
       <c r="AG8">
-        <v>1.71</v>
+        <v>2.85</v>
       </c>
       <c r="AH8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AI8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ8" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="AK8" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL8">
-        <v>1.13</v>
-      </c>
-      <c r="AM8">
-        <v>1.15</v>
-      </c>
-      <c r="AN8">
-        <v>1.05</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>3.4</v>
-      </c>
-      <c r="BC8">
-        <v>1.34</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45804.5</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45804</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L9">
-        <v>2.33</v>
+        <v>11.56</v>
       </c>
       <c r="M9">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="O9">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="T9">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="U9">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W9">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z9">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC9">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AE9">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AF9">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AI9">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="AK9" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL9">
-        <v>1.25</v>
-      </c>
-      <c r="AM9">
-        <v>1.25</v>
-      </c>
-      <c r="AN9">
-        <v>1.57</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.9</v>
-      </c>
-      <c r="BC9">
-        <v>1.95</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>122</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45804.5</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45804</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L10">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="M10">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="N10">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
         <v>2.27</v>
@@ -2326,165 +1864,111 @@
         <v>1.86</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S10">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="T10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
         <v>1.25</v>
       </c>
       <c r="V10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA10">
         <v>2.3</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AC10">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AD10">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AI10">
         <v>1.04</v>
       </c>
       <c r="AJ10" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="AK10" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL10">
-        <v>1.4</v>
-      </c>
-      <c r="AM10">
-        <v>1.3</v>
-      </c>
-      <c r="AN10">
-        <v>1.62</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.59</v>
-      </c>
-      <c r="AQ10">
-        <v>1.98</v>
-      </c>
-      <c r="AR10">
-        <v>3.15</v>
-      </c>
-      <c r="AS10">
-        <v>3.38</v>
-      </c>
-      <c r="AT10">
-        <v>4.65</v>
-      </c>
-      <c r="AU10">
-        <v>2.28</v>
-      </c>
-      <c r="AV10">
-        <v>1.77</v>
-      </c>
-      <c r="AW10">
-        <v>1.46</v>
-      </c>
-      <c r="AX10">
-        <v>1.25</v>
-      </c>
-      <c r="AY10">
-        <v>1.14</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>2.27</v>
-      </c>
-      <c r="BC10">
-        <v>1.86</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>123</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45804.54166666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45804</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L11">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
         <v>1.53</v>
@@ -2496,141 +1980,87 @@
         <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="U11">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="W11">
         <v>1.14</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA11">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AB11">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AD11">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AE11">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AI11">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL11">
-        <v>1.22</v>
-      </c>
-      <c r="AM11">
-        <v>1.21</v>
-      </c>
-      <c r="AN11">
-        <v>2.54</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.53</v>
-      </c>
-      <c r="BC11">
-        <v>2.5</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>124</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45804.54166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45804</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2645,502 +2075,340 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L12">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="M12">
-        <v>3.83</v>
+        <v>3.39</v>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>2.67</v>
       </c>
       <c r="O12">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="P12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V12">
-        <v>5.6</v>
+        <v>6.15</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
+        <v>1.94</v>
+      </c>
+      <c r="AD12">
+        <v>3</v>
+      </c>
+      <c r="AE12">
+        <v>1.4</v>
+      </c>
+      <c r="AF12">
+        <v>1.62</v>
+      </c>
+      <c r="AG12">
         <v>2.1</v>
       </c>
-      <c r="AD12">
-        <v>2.7</v>
-      </c>
-      <c r="AE12">
-        <v>1.48</v>
-      </c>
-      <c r="AF12">
-        <v>1.65</v>
-      </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
       <c r="AH12">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL12">
-        <v>1.18</v>
-      </c>
-      <c r="AM12">
-        <v>1.2</v>
-      </c>
-      <c r="AN12">
-        <v>2.2</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.17</v>
-      </c>
-      <c r="AQ12">
-        <v>1.3</v>
-      </c>
-      <c r="AR12">
-        <v>1.49</v>
-      </c>
-      <c r="AS12">
-        <v>1.77</v>
-      </c>
-      <c r="AT12">
-        <v>2.17</v>
-      </c>
-      <c r="AU12">
-        <v>4.35</v>
-      </c>
-      <c r="AV12">
-        <v>3.15</v>
-      </c>
-      <c r="AW12">
-        <v>2.4</v>
-      </c>
-      <c r="AX12">
-        <v>1.93</v>
-      </c>
-      <c r="AY12">
-        <v>1.6</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.53</v>
-      </c>
-      <c r="BC12">
-        <v>2.8</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45804.58333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45804</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L13">
-        <v>2.22</v>
+        <v>1.58</v>
       </c>
       <c r="M13">
-        <v>3.39</v>
+        <v>3.83</v>
       </c>
       <c r="N13">
-        <v>2.67</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>1.3</v>
+      </c>
+      <c r="S13">
+        <v>3.2</v>
+      </c>
+      <c r="T13">
+        <v>2.4</v>
+      </c>
+      <c r="U13">
+        <v>1.5</v>
+      </c>
+      <c r="V13">
+        <v>5.6</v>
+      </c>
+      <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>11</v>
+      </c>
+      <c r="Z13">
+        <v>1.22</v>
+      </c>
+      <c r="AA13">
+        <v>4.33</v>
+      </c>
+      <c r="AB13">
+        <v>1.65</v>
+      </c>
+      <c r="AC13">
         <v>2.1</v>
       </c>
-      <c r="R13">
-        <v>1.35</v>
-      </c>
-      <c r="S13">
-        <v>2.95</v>
-      </c>
-      <c r="T13">
-        <v>2.62</v>
-      </c>
-      <c r="U13">
-        <v>1.42</v>
-      </c>
-      <c r="V13">
-        <v>6.15</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>10</v>
-      </c>
-      <c r="Z13">
-        <v>1.25</v>
-      </c>
-      <c r="AA13">
-        <v>3.85</v>
-      </c>
-      <c r="AB13">
-        <v>1.76</v>
-      </c>
-      <c r="AC13">
-        <v>1.94</v>
-      </c>
       <c r="AD13">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH13">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AI13">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL13">
-        <v>1.42</v>
-      </c>
-      <c r="AM13">
-        <v>1.25</v>
-      </c>
-      <c r="AN13">
-        <v>1.57</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.22</v>
-      </c>
-      <c r="AQ13">
-        <v>1.38</v>
-      </c>
-      <c r="AR13">
-        <v>1.61</v>
-      </c>
-      <c r="AS13">
-        <v>1.96</v>
-      </c>
-      <c r="AT13">
-        <v>2.43</v>
-      </c>
-      <c r="AU13">
-        <v>3.8</v>
-      </c>
-      <c r="AV13">
-        <v>2.8</v>
-      </c>
-      <c r="AW13">
-        <v>2.15</v>
-      </c>
-      <c r="AX13">
-        <v>1.74</v>
-      </c>
-      <c r="AY13">
-        <v>1.49</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.9</v>
-      </c>
-      <c r="BC13">
-        <v>2.1</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>125</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45804.58333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45804</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>89</v>
-      </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L14">
-        <v>3.45</v>
+        <v>1.38</v>
       </c>
       <c r="M14">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N14">
-        <v>1.88</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
+        <v>17.75</v>
+      </c>
+      <c r="Q14">
+        <v>4.15</v>
+      </c>
+      <c r="R14">
+        <v>1.36</v>
+      </c>
+      <c r="S14">
+        <v>2.9</v>
+      </c>
+      <c r="T14">
+        <v>2.7</v>
+      </c>
+      <c r="U14">
+        <v>1.39</v>
+      </c>
+      <c r="V14">
+        <v>7</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
         <v>9</v>
       </c>
-      <c r="Q14">
-        <v>1.75</v>
-      </c>
-      <c r="R14">
-        <v>1.52</v>
-      </c>
-      <c r="S14">
-        <v>2.3</v>
-      </c>
-      <c r="T14">
-        <v>3.4</v>
-      </c>
-      <c r="U14">
-        <v>1.27</v>
-      </c>
-      <c r="V14">
-        <v>9</v>
-      </c>
-      <c r="W14">
-        <v>1.04</v>
-      </c>
-      <c r="X14">
-        <v>1.11</v>
-      </c>
-      <c r="Y14">
-        <v>6.55</v>
-      </c>
       <c r="Z14">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AA14">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AB14">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC14">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD14">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF14">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH14">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="AI14">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="AK14" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL14">
-        <v>1.4</v>
-      </c>
-      <c r="AM14">
-        <v>1.27</v>
-      </c>
-      <c r="AN14">
-        <v>1.36</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>2.4</v>
-      </c>
-      <c r="BC14">
-        <v>1.75</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>125</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45804.625</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45804</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3155,177 +2423,123 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L15">
-        <v>1.22</v>
+        <v>3.84</v>
       </c>
       <c r="M15">
-        <v>5.3</v>
+        <v>2.85</v>
       </c>
       <c r="N15">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="P15">
-        <v>17.75</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>4.15</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="V15">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA15">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>2.59</v>
       </c>
       <c r="AC15">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="AD15">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="AE15">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>5.75</v>
+        <v>13</v>
       </c>
       <c r="AI15">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL15">
-        <v>1.25</v>
-      </c>
-      <c r="AM15">
-        <v>1.12</v>
-      </c>
-      <c r="AN15">
-        <v>2.25</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.38</v>
-      </c>
-      <c r="AQ15">
-        <v>1.73</v>
-      </c>
-      <c r="AR15">
-        <v>2.23</v>
-      </c>
-      <c r="AS15">
-        <v>3</v>
-      </c>
-      <c r="AT15">
-        <v>4</v>
-      </c>
-      <c r="AU15">
-        <v>2.8</v>
-      </c>
-      <c r="AV15">
-        <v>1.99</v>
-      </c>
-      <c r="AW15">
-        <v>1.58</v>
-      </c>
-      <c r="AX15">
-        <v>1.34</v>
-      </c>
-      <c r="AY15">
-        <v>1.19</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.22</v>
-      </c>
-      <c r="BC15">
-        <v>4.15</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45804.625</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45804</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L16">
         <v>1.64</v>
@@ -3400,442 +2614,280 @@
         <v>1.05</v>
       </c>
       <c r="AJ16" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="AK16" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL16">
-        <v>1.17</v>
-      </c>
-      <c r="AM16">
-        <v>1.28</v>
-      </c>
-      <c r="AN16">
-        <v>2.05</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>1.41</v>
-      </c>
-      <c r="AQ16">
-        <v>1.72</v>
-      </c>
-      <c r="AR16">
-        <v>2.15</v>
-      </c>
-      <c r="AS16">
-        <v>2.75</v>
-      </c>
-      <c r="AT16">
-        <v>3.65</v>
-      </c>
-      <c r="AU16">
-        <v>2.65</v>
-      </c>
-      <c r="AV16">
-        <v>1.98</v>
-      </c>
-      <c r="AW16">
-        <v>1.61</v>
-      </c>
-      <c r="AX16">
-        <v>1.38</v>
-      </c>
-      <c r="AY16">
-        <v>1.22</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.5</v>
-      </c>
-      <c r="BC16">
-        <v>3.25</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>126</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45804.79166666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45804</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L17">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M17">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N17">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
-        <v>8.25</v>
+        <v>7.25</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S17">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AA17">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD17">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH17">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AK17" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL17">
-        <v>1.19</v>
-      </c>
-      <c r="AM17">
-        <v>1.28</v>
-      </c>
-      <c r="AN17">
-        <v>2</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.41</v>
-      </c>
-      <c r="AQ17">
-        <v>1.68</v>
-      </c>
-      <c r="AR17">
-        <v>2.1</v>
-      </c>
-      <c r="AS17">
-        <v>2.7</v>
-      </c>
-      <c r="AT17">
-        <v>3.55</v>
-      </c>
-      <c r="AU17">
-        <v>2.65</v>
-      </c>
-      <c r="AV17">
-        <v>2.02</v>
-      </c>
-      <c r="AW17">
-        <v>1.63</v>
-      </c>
-      <c r="AX17">
-        <v>1.4</v>
-      </c>
-      <c r="AY17">
-        <v>1.24</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.5</v>
-      </c>
-      <c r="BC17">
-        <v>2.88</v>
-      </c>
-      <c r="BD17" s="3">
-        <v>45804.79166666666</v>
+        <v>106</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>45804.8125</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45804</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="E18" t="s">
-        <v>93</v>
-      </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L18">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M18">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O18">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P18">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
       </c>
       <c r="R18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V18">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
+        <v>8.5</v>
+      </c>
+      <c r="Z18">
+        <v>1.35</v>
+      </c>
+      <c r="AA18">
+        <v>3.1</v>
+      </c>
+      <c r="AB18">
+        <v>1.95</v>
+      </c>
+      <c r="AC18">
+        <v>1.75</v>
+      </c>
+      <c r="AD18">
+        <v>3.7</v>
+      </c>
+      <c r="AE18">
+        <v>1.25</v>
+      </c>
+      <c r="AF18">
+        <v>1.95</v>
+      </c>
+      <c r="AG18">
+        <v>1.8</v>
+      </c>
+      <c r="AH18">
+        <v>7.5</v>
+      </c>
+      <c r="AI18">
         <v>1.08</v>
       </c>
-      <c r="Y18">
-        <v>7.5</v>
-      </c>
-      <c r="Z18">
-        <v>1.37</v>
-      </c>
-      <c r="AA18">
-        <v>2.7</v>
-      </c>
-      <c r="AB18">
-        <v>2.3</v>
-      </c>
-      <c r="AC18">
-        <v>1.57</v>
-      </c>
-      <c r="AD18">
-        <v>4</v>
-      </c>
-      <c r="AE18">
-        <v>1.18</v>
-      </c>
-      <c r="AF18">
-        <v>1.87</v>
-      </c>
-      <c r="AG18">
-        <v>1.77</v>
-      </c>
-      <c r="AH18">
-        <v>8.5</v>
-      </c>
-      <c r="AI18">
-        <v>1.06</v>
-      </c>
       <c r="AJ18" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL18">
-        <v>1.33</v>
-      </c>
-      <c r="AM18">
-        <v>1.31</v>
-      </c>
-      <c r="AN18">
-        <v>1.85</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>1.22</v>
-      </c>
-      <c r="AQ18">
-        <v>1.43</v>
-      </c>
-      <c r="AR18">
-        <v>1.7</v>
-      </c>
-      <c r="AS18">
-        <v>2.1</v>
-      </c>
-      <c r="AT18">
-        <v>2.62</v>
-      </c>
-      <c r="AU18">
-        <v>3.6</v>
-      </c>
-      <c r="AV18">
-        <v>2.78</v>
-      </c>
-      <c r="AW18">
-        <v>2.05</v>
-      </c>
-      <c r="AX18">
-        <v>1.67</v>
-      </c>
-      <c r="AY18">
-        <v>1.42</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.57</v>
-      </c>
-      <c r="BC18">
-        <v>2.88</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>127</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45804.8125</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45804</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L19">
         <v>1.75</v>
@@ -3910,162 +2962,108 @@
         <v>1.12</v>
       </c>
       <c r="AJ19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AK19" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL19">
-        <v>1.23</v>
-      </c>
-      <c r="AM19">
-        <v>1.26</v>
-      </c>
-      <c r="AN19">
-        <v>1.93</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>1.3</v>
-      </c>
-      <c r="AQ19">
-        <v>1.53</v>
-      </c>
-      <c r="AR19">
-        <v>1.86</v>
-      </c>
-      <c r="AS19">
-        <v>2.32</v>
-      </c>
-      <c r="AT19">
-        <v>2.9</v>
-      </c>
-      <c r="AU19">
-        <v>3.05</v>
-      </c>
-      <c r="AV19">
-        <v>2.32</v>
-      </c>
-      <c r="AW19">
-        <v>1.82</v>
-      </c>
-      <c r="AX19">
-        <v>1.53</v>
-      </c>
-      <c r="AY19">
-        <v>1.34</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.53</v>
-      </c>
-      <c r="BC19">
-        <v>2.63</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>102</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45804.89583333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45804</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L20">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="M20">
-        <v>4.7</v>
+        <v>3.69</v>
       </c>
       <c r="N20">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="O20">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="Q20">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AA20">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AB20">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC20">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AD20">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE20">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
         <v>2</v>
@@ -4074,108 +3072,54 @@
         <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AJ20" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AK20" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL20">
-        <v>1.07</v>
-      </c>
-      <c r="AM20">
-        <v>1.18</v>
-      </c>
-      <c r="AN20">
-        <v>3.1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>1.23</v>
-      </c>
-      <c r="AQ20">
-        <v>1.4</v>
-      </c>
-      <c r="AR20">
-        <v>1.66</v>
-      </c>
-      <c r="AS20">
-        <v>2.05</v>
-      </c>
-      <c r="AT20">
-        <v>2.55</v>
-      </c>
-      <c r="AU20">
-        <v>3.65</v>
-      </c>
-      <c r="AV20">
-        <v>2.65</v>
-      </c>
-      <c r="AW20">
-        <v>2.06</v>
-      </c>
-      <c r="AX20">
-        <v>1.67</v>
-      </c>
-      <c r="AY20">
-        <v>1.44</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.25</v>
-      </c>
-      <c r="BC20">
-        <v>4.33</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45804.89583333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45804</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L21">
         <v>1.1</v>
@@ -4250,162 +3194,108 @@
         <v>1.25</v>
       </c>
       <c r="AJ21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL21">
-        <v>1.02</v>
-      </c>
-      <c r="AM21">
-        <v>1.08</v>
-      </c>
-      <c r="AN21">
-        <v>5.5</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>1.17</v>
-      </c>
-      <c r="AQ21">
-        <v>1.29</v>
-      </c>
-      <c r="AR21">
-        <v>1.49</v>
-      </c>
-      <c r="AS21">
-        <v>1.77</v>
-      </c>
-      <c r="AT21">
-        <v>2.15</v>
-      </c>
-      <c r="AU21">
-        <v>4.35</v>
-      </c>
-      <c r="AV21">
-        <v>3.15</v>
-      </c>
-      <c r="AW21">
-        <v>2.4</v>
-      </c>
-      <c r="AX21">
-        <v>1.92</v>
-      </c>
-      <c r="AY21">
-        <v>1.61</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.13</v>
-      </c>
-      <c r="BC21">
-        <v>6</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>105</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45804.89583333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45804</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L22">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="M22">
-        <v>3.69</v>
+        <v>4.7</v>
       </c>
       <c r="N22">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="O22">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="P22">
-        <v>8.75</v>
+        <v>11</v>
       </c>
       <c r="Q22">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R22">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S22">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z22">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA22">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB22">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC22">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AD22">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AF22">
         <v>2</v>
@@ -4414,72 +3304,18 @@
         <v>1.75</v>
       </c>
       <c r="AH22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI22">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ22" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL22">
-        <v>1.15</v>
-      </c>
-      <c r="AM22">
-        <v>1.25</v>
-      </c>
-      <c r="AN22">
-        <v>2.25</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>1.28</v>
-      </c>
-      <c r="AQ22">
-        <v>1.48</v>
-      </c>
-      <c r="AR22">
-        <v>1.78</v>
-      </c>
-      <c r="AS22">
-        <v>2.2</v>
-      </c>
-      <c r="AT22">
-        <v>2.8</v>
-      </c>
-      <c r="AU22">
-        <v>3.3</v>
-      </c>
-      <c r="AV22">
-        <v>2.45</v>
-      </c>
-      <c r="AW22">
-        <v>1.91</v>
-      </c>
-      <c r="AX22">
-        <v>1.58</v>
-      </c>
-      <c r="AY22">
-        <v>1.37</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.4</v>
-      </c>
-      <c r="BC22">
-        <v>3.25</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>128</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45804.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-05-27.xlsx
+++ b/jogos_2025-05-27.xlsx
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -927,55 +927,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.72</v>
+        <v>2.01</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>3.07</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
         <v>1.7</v>
@@ -985,25 +985,25 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['17', '45+6', '66', '71']</t>
+          <t>['33', '37', '72']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45804.3125</v>
@@ -1030,81 +1030,81 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="N5" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
         <v>1.7</v>
@@ -1114,25 +1114,25 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['33', '37', '72']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45804.3125</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,55 +1185,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.13</v>
+        <v>3.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
         <v>1.7</v>
@@ -1248,20 +1248,20 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['17', '45+6', '66', '71']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45804.3125</v>
@@ -2074,75 +2074,75 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45804.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,106 +2578,106 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.36</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['45+5', '63']</t>
+          <t>['24', '28']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['28', '42']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ17" t="n">
         <v>2.88</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,106 +2707,106 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['24', '28']</t>
+          <t>['45+5', '63']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['28', '42']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
         <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>2.88</v>
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>14</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>15</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AD20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.15</v>
       </c>
-      <c r="X20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['10', '24']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH20" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45804.89583333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="N21" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>15</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AD21" t="n">
         <v>1.5</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['10', '24']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45804.89583333334</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.69</v>
+        <v>4.7</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AC23" t="n">
         <v>2</v>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45804.89583333334</v>
